--- a/dcf/TECH.xlsx
+++ b/dcf/TECH.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
